--- a/data/example-data-miabis.xlsx
+++ b/data/example-data-miabis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonella\Desktop\bbdataeng\a-small-fhir\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B78B86-1F2C-46E8-9AC8-3A6F197E4582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E883E1F-38F9-431E-A322-67D35F62A58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7903CEA5-AA7C-44DF-9DC5-0F9048285697}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>PATIENT_ID</t>
   </si>
@@ -44,36 +44,12 @@
     <t>SAMPLING_DATE</t>
   </si>
   <si>
-    <t>DONOR_AGE</t>
-  </si>
-  <si>
     <t>SEX</t>
   </si>
   <si>
     <t>SAMPLE_ID</t>
   </si>
   <si>
-    <t>sample-0</t>
-  </si>
-  <si>
-    <t>sample-1</t>
-  </si>
-  <si>
-    <t>sample-2</t>
-  </si>
-  <si>
-    <t>patient-0</t>
-  </si>
-  <si>
-    <t>patient-1</t>
-  </si>
-  <si>
-    <t>C18.9</t>
-  </si>
-  <si>
-    <t>C18.1</t>
-  </si>
-  <si>
     <t>STORAGE_TEMPERATURE</t>
   </si>
   <si>
@@ -86,18 +62,12 @@
     <t>Female</t>
   </si>
   <si>
-    <t>DIAGNOSIS_AGE</t>
-  </si>
-  <si>
     <t>BIRTH_DATE</t>
   </si>
   <si>
     <t>DIAGNOSIS</t>
   </si>
   <si>
-    <t>DATE_DIAGNOSIS</t>
-  </si>
-  <si>
     <t>Room temperature</t>
   </si>
   <si>
@@ -108,6 +78,36 @@
   </si>
   <si>
     <t>Tissue (paraffin preserved)</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS_DATE</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS_DONOR_AGE</t>
+  </si>
+  <si>
+    <t>BB0001</t>
+  </si>
+  <si>
+    <t>PAT0001</t>
+  </si>
+  <si>
+    <t>C18.2</t>
+  </si>
+  <si>
+    <t>BB0002</t>
+  </si>
+  <si>
+    <t>PAT0002</t>
+  </si>
+  <si>
+    <t>BB0003</t>
+  </si>
+  <si>
+    <t>PAT0003</t>
+  </si>
+  <si>
+    <t>C34.9</t>
   </si>
 </sst>
 </file>
@@ -115,9 +115,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,17 +128,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -153,12 +151,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -166,75 +164,43 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{D91F66B7-695D-4F09-BE91-47D488AF2AFC}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -567,161 +533,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB8A45B-4F8B-45BC-A272-7D87119AF989}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="16" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="9">
+        <v>44573</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="9">
+        <v>44573</v>
+      </c>
+      <c r="F2" s="6">
+        <v>62</v>
+      </c>
+      <c r="G2" s="9">
+        <v>25753</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9">
+        <v>44574</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="E3" s="9">
+        <v>44574</v>
+      </c>
+      <c r="F3" s="6">
+        <v>62</v>
+      </c>
+      <c r="G3" s="9">
+        <v>25764</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9">
+        <v>44575</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="9">
+        <v>44575</v>
+      </c>
+      <c r="F4" s="6">
+        <v>62</v>
+      </c>
+      <c r="G4" s="9">
+        <v>29424</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="8">
-        <v>43960</v>
-      </c>
-      <c r="D2" s="8">
-        <v>43960</v>
-      </c>
-      <c r="E2" s="8">
-        <v>13332</v>
-      </c>
-      <c r="F2" s="2">
-        <v>80</v>
-      </c>
-      <c r="G2" s="2">
-        <v>80</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="8">
-        <v>43960</v>
-      </c>
-      <c r="D3" s="8">
-        <v>43960</v>
-      </c>
-      <c r="E3" s="8">
-        <v>13332</v>
-      </c>
-      <c r="F3" s="2">
-        <v>82</v>
-      </c>
-      <c r="G3" s="2">
-        <v>82</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="8">
-        <v>43960</v>
-      </c>
-      <c r="D4" s="8">
-        <v>43960</v>
-      </c>
-      <c r="E4" s="8">
-        <v>14097</v>
-      </c>
-      <c r="F4" s="2">
-        <v>80</v>
-      </c>
-      <c r="G4" s="2">
-        <v>80</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
